--- a/ValueSet-ACCESSMSKClinicalExclusionDiagnosisVS.xlsx
+++ b/ValueSet-ACCESSMSKClinicalExclusionDiagnosisVS.xlsx
@@ -153,7 +153,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T22:54:52-04:00</t>
+    <t>2026-06-04T23:05:21-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ACCESSMSKClinicalExclusionDiagnosisVS.xlsx
+++ b/ValueSet-ACCESSMSKClinicalExclusionDiagnosisVS.xlsx
@@ -123,7 +123,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.11</t>
+    <t>0.9.12</t>
   </si>
   <si>
     <t>Name</t>
@@ -153,7 +153,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T23:05:21-04:00</t>
+    <t>2026-06-10T23:08:55-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
